--- a/ELW2024/ELW2024_発表論文公開承諾書.xlsx
+++ b/ELW2024/ELW2024_発表論文公開承諾書.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masayu-a\OneDrive - NINJAL\ドキュメント\GitHub\ELW\ELW2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ninjal-my.sharepoint.com/personal/masayu-a_ninjal_ac_jp/Documents/デスクトップ/ELW/ELW2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_568FC794A57B44B077B6B1C0B2EA0666D89F31F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F423B50-52D3-4C84-85F2-5938D0B73B13}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20570" windowHeight="9190"/>
+    <workbookView xWindow="-76910" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="論文メタデータ" sheetId="1" r:id="rId1"/>
@@ -181,7 +182,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Evidence-based Linguistics Workshop 2023 に投稿した以下の発表論文について、以下の扱いを承諾する。
+    <t>Evidence-based Linguistics Workshop 2024 に投稿した以下の発表論文について、以下の扱いを承諾する。
 ・論文の著作権は著者に帰属する
 ・著者は、同論文をクリエイティブコモンズ 4.0 表示 (CC BY 4.0) のもと、国立国語研究所が国立国語研究所機関リポジトリにて公開することを許諾する
 ・国立国語研究所の機関リポジトリ登録にともない、抄録を含めた同論文のメタデータの自由利用（複製、翻訳、再配布等）を認める</t>
@@ -281,7 +282,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -349,23 +350,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -668,362 +660,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="3" width="66.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="249.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:20" ht="249.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-    </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="10">
+      <c r="B5" s="5"/>
+      <c r="C5" s="7">
         <v>45146</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="6"/>
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="6"/>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:20" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="6"/>
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="4"/>
+      <c r="T10" s="2"/>
     </row>
     <row r="11" spans="1:20" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:20" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="6"/>
+      <c r="C13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:20" ht="180" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1037,7 +839,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
@@ -1093,6 +895,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010084F48AE92D7C994BA1FFFB5EC0217B44" ma:contentTypeVersion="29" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c1ece492b088b728ddc229bb90f269bb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f3f512d3-6195-4655-8eda-4b4a84e395f6" xmlns:ns4="e56da3c0-a9e1-42c3-99ce-a9b98a1dde41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e11460e12859cbbd19c5a12eafaba3f" ns3:_="" ns4:_="">
     <xsd:import namespace="f3f512d3-6195-4655-8eda-4b4a84e395f6"/>
@@ -1475,15 +1286,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72F3867-CC1F-439F-86D6-7D75107B8029}">
   <ds:schemaRefs>
@@ -1502,6 +1304,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A5C0875-96D2-40B8-96FC-BBC6F745AEF0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1518,12 +1328,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0234DF2-6DDD-4E33-964F-7B49E9A391E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>